--- a/ЛР5_Анализ_конкурентов/Excel/ЛР5_3_бизнес_модели_конкурентов_TableMind.xlsx
+++ b/ЛР5_Анализ_конкурентов/Excel/ЛР5_3_бизнес_модели_конкурентов_TableMind.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TableMind_EB\.claude\worktrees\handoff-continuation-3ab569\ЛР5_Анализ_конкурентов\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TableMind_EB\.claude\worktrees\handoff-continuation-57ce20\ЛР5_Анализ_конкурентов\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37331242-C367-402E-955B-98B70D74DDB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{512A1526-1D99-4063-9944-736D77BA1587}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="368" yWindow="368" windowWidth="12022" windowHeight="10972" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1073" uniqueCount="685">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1073" uniqueCount="694">
   <si>
     <t>Справочники для раскрывающихся списков</t>
   </si>
@@ -1131,7 +1131,7 @@
     <t>загрузка и активация, справка</t>
   </si>
   <si>
-    <t>лицензия (цена не показана)</t>
+    <t>лицензия 2,75 GBP за пользователя в месяц (срок 12-36 месяцев)</t>
   </si>
   <si>
     <t>надстройка, малая команда</t>
@@ -1152,7 +1152,28 @@
     <t>Arixcel Explorer: логика формул, сравнение таблиц, карта формул, трассировка зависимых ячеек</t>
   </si>
   <si>
-    <t>Цена скрыта, высокий барьер первого шага</t>
+    <t>arixcel.com/explorer/download</t>
+  </si>
+  <si>
+    <t>да (пробный режим)</t>
+  </si>
+  <si>
+    <t>одна лицензия</t>
+  </si>
+  <si>
+    <t>пользователь в месяц</t>
+  </si>
+  <si>
+    <t>срок 12-36 месяцев</t>
+  </si>
+  <si>
+    <t>месяц, срок 12-36 месяцев</t>
+  </si>
+  <si>
+    <t>да (многопользовательская)</t>
+  </si>
+  <si>
+    <t>Цена опубликована (2,75 GBP), но лестницы тарифов и бесплатного входа нет</t>
   </si>
   <si>
     <t>прямой, органика</t>
@@ -1248,16 +1269,25 @@
     <t>услуги + лицензия</t>
   </si>
   <si>
+    <t>operisanalysiskit.com/oak-price</t>
+  </si>
+  <si>
+    <t>да (30 дней по запросу)</t>
+  </si>
+  <si>
     <t>проект, лицензия OAK</t>
   </si>
   <si>
-    <t>проект</t>
-  </si>
-  <si>
-    <t>разово</t>
-  </si>
-  <si>
-    <t>Продажа через консультанта, не самообслуживание</t>
+    <t>проект, пользователь</t>
+  </si>
+  <si>
+    <t>налог сверх цены</t>
+  </si>
+  <si>
+    <t>год</t>
+  </si>
+  <si>
+    <t>Цена OAK опубликована (311,66 GBP в год), услуги аудита продаются через консультанта</t>
   </si>
   <si>
     <t>прямой, органика, соцсети</t>
@@ -1501,9 +1531,6 @@
   </si>
   <si>
     <t>500 тыс. символов и 500 генераций</t>
-  </si>
-  <si>
-    <t>год</t>
   </si>
   <si>
     <t>да (от 8 пользователей)</t>
@@ -2411,7 +2438,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-2C06-402D-B599-3D00D8E0A963}"/>
+              <c16:uniqueId val="{00000000-C507-44E1-BB60-FBFA8A9F5124}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3475,7 +3502,7 @@
     </row>
     <row r="6" spans="1:26">
       <c r="A6" s="2" t="s">
-        <v>380</v>
+        <v>387</v>
       </c>
       <c r="B6" s="5" t="str">
         <f>IF($A6="","",IFERROR(VLOOKUP($A6,'02_Конкуренты'!$A$4:$B$203,2,FALSE),"не найдено"))</f>
@@ -3533,7 +3560,7 @@
     </row>
     <row r="7" spans="1:26">
       <c r="A7" s="2" t="s">
-        <v>421</v>
+        <v>431</v>
       </c>
       <c r="B7" s="5" t="str">
         <f>IF($A7="","",IFERROR(VLOOKUP($A7,'02_Конкуренты'!$A$4:$B$203,2,FALSE),"не найдено"))</f>
@@ -3591,7 +3618,7 @@
     </row>
     <row r="8" spans="1:26">
       <c r="A8" s="2" t="s">
-        <v>464</v>
+        <v>474</v>
       </c>
       <c r="B8" s="5" t="str">
         <f>IF($A8="","",IFERROR(VLOOKUP($A8,'02_Конкуренты'!$A$4:$B$203,2,FALSE),"не найдено"))</f>
@@ -3649,7 +3676,7 @@
     </row>
     <row r="9" spans="1:26">
       <c r="A9" s="2" t="s">
-        <v>505</v>
+        <v>514</v>
       </c>
       <c r="B9" s="5" t="str">
         <f>IF($A9="","",IFERROR(VLOOKUP($A9,'02_Конкуренты'!$A$4:$B$203,2,FALSE),"не найдено"))</f>
@@ -3707,7 +3734,7 @@
     </row>
     <row r="10" spans="1:26">
       <c r="A10" s="2" t="s">
-        <v>547</v>
+        <v>556</v>
       </c>
       <c r="B10" s="5" t="str">
         <f>IF($A10="","",IFERROR(VLOOKUP($A10,'02_Конкуренты'!$A$4:$B$203,2,FALSE),"не найдено"))</f>
@@ -10436,13 +10463,13 @@
     </row>
     <row r="4" spans="1:26" ht="27">
       <c r="A4" s="2" t="s">
-        <v>641</v>
+        <v>650</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>155</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>642</v>
+        <v>651</v>
       </c>
       <c r="D4" s="2">
         <v>7</v>
@@ -10460,18 +10487,18 @@
         <v>необходимо включить в минимально приемлемое предложение</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>643</v>
+        <v>652</v>
       </c>
     </row>
     <row r="5" spans="1:26" ht="27">
       <c r="A5" s="2" t="s">
-        <v>644</v>
+        <v>653</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>158</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>645</v>
+        <v>654</v>
       </c>
       <c r="D5" s="2">
         <v>2</v>
@@ -10489,18 +10516,18 @@
         <v>может использоваться как поле позиционирования</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>643</v>
+        <v>652</v>
       </c>
     </row>
     <row r="6" spans="1:26" ht="27">
       <c r="A6" s="2" t="s">
-        <v>646</v>
+        <v>655</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>157</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>647</v>
+        <v>656</v>
       </c>
       <c r="D6" s="2">
         <v>3</v>
@@ -10518,18 +10545,18 @@
         <v>проверить значимость для клиента и вероятность закрепления</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>643</v>
+        <v>652</v>
       </c>
     </row>
     <row r="7" spans="1:26" ht="27">
       <c r="A7" s="2" t="s">
-        <v>648</v>
+        <v>657</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>156</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>649</v>
+        <v>658</v>
       </c>
       <c r="D7" s="2">
         <v>4</v>
@@ -10547,18 +10574,18 @@
         <v>проверить значимость для клиента и вероятность закрепления</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>643</v>
+        <v>652</v>
       </c>
     </row>
     <row r="8" spans="1:26" ht="27">
       <c r="A8" s="2" t="s">
-        <v>650</v>
+        <v>659</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>159</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>651</v>
+        <v>660</v>
       </c>
       <c r="D8" s="2">
         <v>3</v>
@@ -10576,18 +10603,18 @@
         <v>проверить значимость для клиента и вероятность закрепления</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>643</v>
+        <v>652</v>
       </c>
     </row>
     <row r="9" spans="1:26">
       <c r="A9" s="2" t="s">
-        <v>652</v>
+        <v>661</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>154</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>653</v>
+        <v>662</v>
       </c>
       <c r="D9" s="2">
         <v>5</v>
@@ -10605,18 +10632,18 @@
         <v>необходимо включить в минимально приемлемое предложение</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>643</v>
+        <v>652</v>
       </c>
     </row>
     <row r="10" spans="1:26">
       <c r="A10" s="2" t="s">
-        <v>654</v>
+        <v>663</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>158</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>655</v>
+        <v>664</v>
       </c>
       <c r="D10" s="2">
         <v>5</v>
@@ -10634,18 +10661,18 @@
         <v>необходимо включить в минимально приемлемое предложение</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>643</v>
+        <v>652</v>
       </c>
     </row>
     <row r="11" spans="1:26">
       <c r="A11" s="2" t="s">
-        <v>656</v>
+        <v>665</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>157</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>657</v>
+        <v>666</v>
       </c>
       <c r="D11" s="2">
         <v>6</v>
@@ -10663,18 +10690,18 @@
         <v>необходимо включить в минимально приемлемое предложение</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>643</v>
+        <v>652</v>
       </c>
     </row>
     <row r="12" spans="1:26">
       <c r="A12" s="2" t="s">
-        <v>658</v>
+        <v>667</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>155</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>659</v>
+        <v>668</v>
       </c>
       <c r="D12" s="2">
         <v>4</v>
@@ -10692,18 +10719,18 @@
         <v>проверить значимость для клиента и вероятность закрепления</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>643</v>
+        <v>652</v>
       </c>
     </row>
     <row r="13" spans="1:26" ht="27">
       <c r="A13" s="2" t="s">
-        <v>660</v>
+        <v>669</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>155</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>661</v>
+        <v>670</v>
       </c>
       <c r="D13" s="2">
         <v>2</v>
@@ -10721,18 +10748,18 @@
         <v>может использоваться как поле позиционирования</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>643</v>
+        <v>652</v>
       </c>
     </row>
     <row r="14" spans="1:26" ht="27">
       <c r="A14" s="2" t="s">
-        <v>662</v>
+        <v>671</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>158</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>663</v>
+        <v>672</v>
       </c>
       <c r="D14" s="2">
         <v>4</v>
@@ -10750,18 +10777,18 @@
         <v>проверить значимость для клиента и вероятность закрепления</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>643</v>
+        <v>652</v>
       </c>
     </row>
     <row r="15" spans="1:26">
       <c r="A15" s="2" t="s">
-        <v>664</v>
+        <v>673</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>161</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>665</v>
+        <v>674</v>
       </c>
       <c r="D15" s="2">
         <v>4</v>
@@ -10779,7 +10806,7 @@
         <v>проверить значимость для клиента и вероятность закрепления</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>643</v>
+        <v>652</v>
       </c>
     </row>
     <row r="16" spans="1:26">
@@ -14499,16 +14526,16 @@
         <v>PerfectXL</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>666</v>
+        <v>675</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>667</v>
+        <v>676</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>154</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>668</v>
+        <v>677</v>
       </c>
       <c r="G4" s="2">
         <v>4</v>
@@ -14531,7 +14558,7 @@
         <v>умеренное преимущество</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>669</v>
+        <v>678</v>
       </c>
     </row>
     <row r="5" spans="1:26" ht="27">
@@ -14543,7 +14570,7 @@
         <v>PerfectXL</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>670</v>
+        <v>679</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>19</v>
@@ -14552,7 +14579,7 @@
         <v>155</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>671</v>
+        <v>680</v>
       </c>
       <c r="G5" s="2">
         <v>4</v>
@@ -14575,28 +14602,28 @@
         <v>умеренное преимущество</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>669</v>
+        <v>678</v>
       </c>
     </row>
     <row r="6" spans="1:26" ht="27">
       <c r="A6" s="2" t="s">
-        <v>421</v>
+        <v>431</v>
       </c>
       <c r="B6" s="5" t="str">
         <f>IF($A6="","",IFERROR(VLOOKUP($A6,'02_Конкуренты'!$A$4:$B$203,2,FALSE),"не найдено"))</f>
         <v>Shortcut</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>672</v>
+        <v>681</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>673</v>
+        <v>682</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>158</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>440</v>
+        <v>450</v>
       </c>
       <c r="G6" s="2">
         <v>4</v>
@@ -14619,28 +14646,28 @@
         <v>умеренное преимущество</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>669</v>
+        <v>678</v>
       </c>
     </row>
     <row r="7" spans="1:26" ht="27">
       <c r="A7" s="2" t="s">
-        <v>421</v>
+        <v>431</v>
       </c>
       <c r="B7" s="5" t="str">
         <f>IF($A7="","",IFERROR(VLOOKUP($A7,'02_Конкуренты'!$A$4:$B$203,2,FALSE),"не найдено"))</f>
         <v>Shortcut</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>674</v>
+        <v>683</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>667</v>
+        <v>676</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>675</v>
+        <v>684</v>
       </c>
       <c r="G7" s="2">
         <v>5</v>
@@ -14663,19 +14690,19 @@
         <v>сильное преимущество</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>669</v>
+        <v>678</v>
       </c>
     </row>
     <row r="8" spans="1:26" ht="27">
       <c r="A8" s="2" t="s">
-        <v>464</v>
+        <v>474</v>
       </c>
       <c r="B8" s="5" t="str">
         <f>IF($A8="","",IFERROR(VLOOKUP($A8,'02_Конкуренты'!$A$4:$B$203,2,FALSE),"не найдено"))</f>
         <v>Numerous.ai</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>676</v>
+        <v>685</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>28</v>
@@ -14684,7 +14711,7 @@
         <v>158</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>480</v>
+        <v>490</v>
       </c>
       <c r="G8" s="2">
         <v>3</v>
@@ -14707,28 +14734,28 @@
         <v>слабое преимущество</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>669</v>
+        <v>678</v>
       </c>
     </row>
     <row r="9" spans="1:26" ht="27">
       <c r="A9" s="2" t="s">
-        <v>505</v>
+        <v>514</v>
       </c>
       <c r="B9" s="5" t="str">
         <f>IF($A9="","",IFERROR(VLOOKUP($A9,'02_Конкуренты'!$A$4:$B$203,2,FALSE),"не найдено"))</f>
         <v>Datarails</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>677</v>
+        <v>686</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>678</v>
+        <v>687</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>161</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>679</v>
+        <v>688</v>
       </c>
       <c r="G9" s="2">
         <v>5</v>
@@ -14751,28 +14778,28 @@
         <v>сильное преимущество</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>669</v>
+        <v>678</v>
       </c>
     </row>
     <row r="10" spans="1:26" ht="27">
       <c r="A10" s="2" t="s">
-        <v>547</v>
+        <v>556</v>
       </c>
       <c r="B10" s="5" t="str">
         <f>IF($A10="","",IFERROR(VLOOKUP($A10,'02_Конкуренты'!$A$4:$B$203,2,FALSE),"не найдено"))</f>
         <v>DataSnipper</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>680</v>
+        <v>689</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>667</v>
+        <v>676</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>154</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>681</v>
+        <v>690</v>
       </c>
       <c r="G10" s="2">
         <v>5</v>
@@ -14795,28 +14822,28 @@
         <v>сильное преимущество</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>669</v>
+        <v>678</v>
       </c>
     </row>
     <row r="11" spans="1:26" ht="27">
       <c r="A11" s="2" t="s">
-        <v>380</v>
+        <v>387</v>
       </c>
       <c r="B11" s="5" t="str">
         <f>IF($A11="","",IFERROR(VLOOKUP($A11,'02_Конкуренты'!$A$4:$B$203,2,FALSE),"не найдено"))</f>
         <v>Operis</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>682</v>
+        <v>691</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>683</v>
+        <v>692</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>154</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>684</v>
+        <v>693</v>
       </c>
       <c r="G11" s="2">
         <v>4</v>
@@ -14839,7 +14866,7 @@
         <v>сильное преимущество</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>669</v>
+        <v>678</v>
       </c>
     </row>
     <row r="12" spans="1:26">
@@ -20349,22 +20376,22 @@
     </row>
     <row r="6" spans="1:26" ht="40.5">
       <c r="A6" s="3" t="s">
-        <v>380</v>
+        <v>387</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>381</v>
+        <v>388</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>382</v>
+        <v>389</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>383</v>
+        <v>390</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>11</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>384</v>
+        <v>391</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>12</v>
@@ -20384,22 +20411,22 @@
     </row>
     <row r="7" spans="1:26" ht="40.5">
       <c r="A7" s="3" t="s">
-        <v>421</v>
+        <v>431</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>422</v>
+        <v>432</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>423</v>
+        <v>433</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>424</v>
+        <v>434</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>425</v>
+        <v>435</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>426</v>
+        <v>436</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>12</v>
@@ -20419,22 +20446,22 @@
     </row>
     <row r="8" spans="1:26" ht="40.5">
       <c r="A8" s="3" t="s">
-        <v>464</v>
+        <v>474</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>465</v>
+        <v>475</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>466</v>
+        <v>476</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>467</v>
+        <v>477</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>29</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>426</v>
+        <v>436</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>12</v>
@@ -20454,22 +20481,22 @@
     </row>
     <row r="9" spans="1:26" ht="54">
       <c r="A9" s="3" t="s">
-        <v>505</v>
+        <v>514</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>506</v>
+        <v>515</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>507</v>
+        <v>516</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>508</v>
+        <v>517</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>29</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>509</v>
+        <v>518</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>12</v>
@@ -20489,19 +20516,19 @@
     </row>
     <row r="10" spans="1:26" ht="54">
       <c r="A10" s="3" t="s">
-        <v>547</v>
+        <v>556</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>548</v>
+        <v>557</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>549</v>
+        <v>558</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>550</v>
+        <v>559</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>425</v>
+        <v>435</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>297</v>
@@ -23157,7 +23184,7 @@
     </row>
     <row r="4" spans="1:26" ht="27">
       <c r="A4" s="2" t="s">
-        <v>581</v>
+        <v>590</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>293</v>
@@ -23167,16 +23194,16 @@
         <v>PerfectXL</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>582</v>
+        <v>591</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>295</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>582</v>
+        <v>591</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>583</v>
+        <v>592</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>23</v>
@@ -23188,15 +23215,15 @@
         <v>46298</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>584</v>
+        <v>593</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>585</v>
+        <v>594</v>
       </c>
     </row>
     <row r="5" spans="1:26" ht="27">
       <c r="A5" s="2" t="s">
-        <v>586</v>
+        <v>595</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>293</v>
@@ -23206,16 +23233,16 @@
         <v>PerfectXL</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>587</v>
+        <v>596</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>588</v>
+        <v>597</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>587</v>
+        <v>596</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>589</v>
+        <v>598</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>53</v>
@@ -23227,15 +23254,15 @@
         <v>46298</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>584</v>
+        <v>593</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>590</v>
+        <v>599</v>
       </c>
     </row>
     <row r="6" spans="1:26" ht="27">
       <c r="A6" s="2" t="s">
-        <v>591</v>
+        <v>600</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>351</v>
@@ -23245,16 +23272,16 @@
         <v>Arixcel</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>582</v>
+        <v>591</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>353</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>582</v>
+        <v>591</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>592</v>
+        <v>601</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>23</v>
@@ -23266,34 +23293,34 @@
         <v>46298</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>584</v>
+        <v>593</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>593</v>
+        <v>602</v>
       </c>
     </row>
     <row r="7" spans="1:26" ht="40.5">
       <c r="A7" s="2" t="s">
-        <v>594</v>
+        <v>603</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>380</v>
+        <v>387</v>
       </c>
       <c r="C7" s="5" t="str">
         <f>IF($B7="","",IFERROR(VLOOKUP($B7,'02_Конкуренты'!$A$4:$B$203,2,FALSE),"не найдено"))</f>
         <v>Operis</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>582</v>
+        <v>591</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>382</v>
+        <v>389</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>582</v>
+        <v>591</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>595</v>
+        <v>604</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>23</v>
@@ -23305,34 +23332,34 @@
         <v>46298</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>584</v>
+        <v>593</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>596</v>
+        <v>605</v>
       </c>
     </row>
     <row r="8" spans="1:26" ht="27">
       <c r="A8" s="2" t="s">
-        <v>597</v>
+        <v>606</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>421</v>
+        <v>431</v>
       </c>
       <c r="C8" s="5" t="str">
         <f>IF($B8="","",IFERROR(VLOOKUP($B8,'02_Конкуренты'!$A$4:$B$203,2,FALSE),"не найдено"))</f>
         <v>Shortcut</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>582</v>
+        <v>591</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>423</v>
+        <v>433</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>582</v>
+        <v>591</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>598</v>
+        <v>607</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>23</v>
@@ -23344,34 +23371,34 @@
         <v>46298</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>584</v>
+        <v>593</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>599</v>
+        <v>608</v>
       </c>
     </row>
     <row r="9" spans="1:26" ht="27">
       <c r="A9" s="2" t="s">
-        <v>600</v>
+        <v>609</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>421</v>
+        <v>431</v>
       </c>
       <c r="C9" s="5" t="str">
         <f>IF($B9="","",IFERROR(VLOOKUP($B9,'02_Конкуренты'!$A$4:$B$203,2,FALSE),"не найдено"))</f>
         <v>Shortcut</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>587</v>
+        <v>596</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>601</v>
+        <v>610</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>587</v>
+        <v>596</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>602</v>
+        <v>611</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>53</v>
@@ -23383,34 +23410,34 @@
         <v>46298</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>584</v>
+        <v>593</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>603</v>
+        <v>612</v>
       </c>
     </row>
     <row r="10" spans="1:26" ht="27">
       <c r="A10" s="2" t="s">
-        <v>604</v>
+        <v>613</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>464</v>
+        <v>474</v>
       </c>
       <c r="C10" s="5" t="str">
         <f>IF($B10="","",IFERROR(VLOOKUP($B10,'02_Конкуренты'!$A$4:$B$203,2,FALSE),"не найдено"))</f>
         <v>Numerous.ai</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>582</v>
+        <v>591</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>466</v>
+        <v>476</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>582</v>
+        <v>591</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>605</v>
+        <v>614</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>23</v>
@@ -23422,34 +23449,34 @@
         <v>46298</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>584</v>
+        <v>593</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>606</v>
+        <v>615</v>
       </c>
     </row>
     <row r="11" spans="1:26">
       <c r="A11" s="2" t="s">
-        <v>607</v>
+        <v>616</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>464</v>
+        <v>474</v>
       </c>
       <c r="C11" s="5" t="str">
         <f>IF($B11="","",IFERROR(VLOOKUP($B11,'02_Конкуренты'!$A$4:$B$203,2,FALSE),"не найдено"))</f>
         <v>Numerous.ai</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>587</v>
+        <v>596</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>608</v>
+        <v>617</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>587</v>
+        <v>596</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>609</v>
+        <v>618</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>53</v>
@@ -23461,34 +23488,34 @@
         <v>46298</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>584</v>
+        <v>593</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>610</v>
+        <v>619</v>
       </c>
     </row>
     <row r="12" spans="1:26" ht="27">
       <c r="A12" s="2" t="s">
-        <v>611</v>
+        <v>620</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>505</v>
+        <v>514</v>
       </c>
       <c r="C12" s="5" t="str">
         <f>IF($B12="","",IFERROR(VLOOKUP($B12,'02_Конкуренты'!$A$4:$B$203,2,FALSE),"не найдено"))</f>
         <v>Datarails</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>582</v>
+        <v>591</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>507</v>
+        <v>516</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>582</v>
+        <v>591</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>612</v>
+        <v>621</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>23</v>
@@ -23500,34 +23527,34 @@
         <v>46298</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>584</v>
+        <v>593</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>613</v>
+        <v>622</v>
       </c>
     </row>
     <row r="13" spans="1:26" ht="27">
       <c r="A13" s="2" t="s">
-        <v>614</v>
+        <v>623</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>547</v>
+        <v>556</v>
       </c>
       <c r="C13" s="5" t="str">
         <f>IF($B13="","",IFERROR(VLOOKUP($B13,'02_Конкуренты'!$A$4:$B$203,2,FALSE),"не найдено"))</f>
         <v>DataSnipper</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>582</v>
+        <v>591</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>549</v>
+        <v>558</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>582</v>
+        <v>591</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>615</v>
+        <v>624</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>23</v>
@@ -23539,34 +23566,34 @@
         <v>46298</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>584</v>
+        <v>593</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>616</v>
+        <v>625</v>
       </c>
     </row>
     <row r="14" spans="1:26" ht="27">
       <c r="A14" s="2" t="s">
-        <v>617</v>
+        <v>626</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>421</v>
+        <v>431</v>
       </c>
       <c r="C14" s="5" t="str">
         <f>IF($B14="","",IFERROR(VLOOKUP($B14,'02_Конкуренты'!$A$4:$B$203,2,FALSE),"не найдено"))</f>
         <v>Shortcut</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>618</v>
+        <v>627</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>619</v>
+        <v>628</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>618</v>
+        <v>627</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>620</v>
+        <v>629</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>47</v>
@@ -23578,34 +23605,34 @@
         <v>46298</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>584</v>
+        <v>593</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>621</v>
+        <v>630</v>
       </c>
     </row>
     <row r="15" spans="1:26" ht="27">
       <c r="A15" s="2" t="s">
-        <v>622</v>
+        <v>631</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>505</v>
+        <v>514</v>
       </c>
       <c r="C15" s="5" t="str">
         <f>IF($B15="","",IFERROR(VLOOKUP($B15,'02_Конкуренты'!$A$4:$B$203,2,FALSE),"не найдено"))</f>
         <v>Datarails</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>618</v>
+        <v>627</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>623</v>
+        <v>632</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>618</v>
+        <v>627</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>624</v>
+        <v>633</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>47</v>
@@ -23617,15 +23644,15 @@
         <v>46298</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>584</v>
+        <v>593</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>625</v>
+        <v>634</v>
       </c>
     </row>
     <row r="16" spans="1:26" ht="27">
       <c r="A16" s="2" t="s">
-        <v>626</v>
+        <v>635</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>293</v>
@@ -23635,16 +23662,16 @@
         <v>PerfectXL</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>618</v>
+        <v>627</v>
       </c>
       <c r="E16" s="2" t="s">
+        <v>636</v>
+      </c>
+      <c r="F16" s="2" t="s">
         <v>627</v>
       </c>
-      <c r="F16" s="2" t="s">
-        <v>618</v>
-      </c>
       <c r="G16" s="2" t="s">
-        <v>628</v>
+        <v>637</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>47</v>
@@ -23656,15 +23683,15 @@
         <v>46298</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>584</v>
+        <v>593</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>621</v>
+        <v>630</v>
       </c>
     </row>
     <row r="17" spans="1:12" ht="27">
       <c r="A17" s="2" t="s">
-        <v>629</v>
+        <v>638</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>351</v>
@@ -23674,16 +23701,16 @@
         <v>Arixcel</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>618</v>
+        <v>627</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>618</v>
+        <v>627</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>631</v>
+        <v>640</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>47</v>
@@ -23695,34 +23722,34 @@
         <v>46298</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>584</v>
+        <v>593</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>632</v>
+        <v>641</v>
       </c>
     </row>
     <row r="18" spans="1:12" ht="27">
       <c r="A18" s="2" t="s">
-        <v>633</v>
+        <v>642</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>380</v>
+        <v>387</v>
       </c>
       <c r="C18" s="5" t="str">
         <f>IF($B18="","",IFERROR(VLOOKUP($B18,'02_Конкуренты'!$A$4:$B$203,2,FALSE),"не найдено"))</f>
         <v>Operis</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>634</v>
+        <v>643</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>635</v>
+        <v>644</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>634</v>
+        <v>643</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>636</v>
+        <v>645</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>40</v>
@@ -23734,34 +23761,34 @@
         <v>46298</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>584</v>
+        <v>593</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>637</v>
+        <v>646</v>
       </c>
     </row>
     <row r="19" spans="1:12" ht="27">
       <c r="A19" s="2" t="s">
-        <v>638</v>
+        <v>647</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>547</v>
+        <v>556</v>
       </c>
       <c r="C19" s="5" t="str">
         <f>IF($B19="","",IFERROR(VLOOKUP($B19,'02_Конкуренты'!$A$4:$B$203,2,FALSE),"не найдено"))</f>
         <v>DataSnipper</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>634</v>
+        <v>643</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>635</v>
+        <v>644</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>634</v>
+        <v>643</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>639</v>
+        <v>648</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>40</v>
@@ -23773,10 +23800,10 @@
         <v>46298</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>584</v>
+        <v>593</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>640</v>
+        <v>649</v>
       </c>
     </row>
     <row r="20" spans="1:12">
@@ -32223,7 +32250,7 @@
         <v>готов к сравнению</v>
       </c>
     </row>
-    <row r="5" spans="1:26" ht="27">
+    <row r="5" spans="1:26" ht="40.5">
       <c r="A5" s="2" t="s">
         <v>351</v>
       </c>
@@ -32282,47 +32309,47 @@
     </row>
     <row r="6" spans="1:26" ht="40.5">
       <c r="A6" s="2" t="s">
-        <v>380</v>
+        <v>387</v>
       </c>
       <c r="B6" s="5" t="str">
         <f>IF($A6="","",IFERROR(VLOOKUP($A6,'02_Конкуренты'!$A$4:$B$203,2,FALSE),"не найдено"))</f>
         <v>Operis</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>385</v>
+        <v>392</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>386</v>
+        <v>393</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>387</v>
+        <v>394</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>388</v>
+        <v>395</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>389</v>
+        <v>396</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>390</v>
+        <v>397</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>391</v>
+        <v>398</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>392</v>
+        <v>399</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>393</v>
+        <v>400</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>394</v>
+        <v>401</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>395</v>
+        <v>402</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>396</v>
+        <v>403</v>
       </c>
       <c r="O6" s="6">
         <f t="shared" si="0"/>
@@ -32339,47 +32366,47 @@
     </row>
     <row r="7" spans="1:26" ht="40.5">
       <c r="A7" s="2" t="s">
-        <v>421</v>
+        <v>431</v>
       </c>
       <c r="B7" s="5" t="str">
         <f>IF($A7="","",IFERROR(VLOOKUP($A7,'02_Конкуренты'!$A$4:$B$203,2,FALSE),"не найдено"))</f>
         <v>Shortcut</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>424</v>
+        <v>434</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>427</v>
+        <v>437</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>428</v>
+        <v>438</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>429</v>
+        <v>439</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>430</v>
+        <v>440</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>431</v>
+        <v>441</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>432</v>
+        <v>442</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>433</v>
+        <v>443</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>434</v>
+        <v>444</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>435</v>
+        <v>445</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>436</v>
+        <v>446</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>437</v>
+        <v>447</v>
       </c>
       <c r="O7" s="6">
         <f t="shared" si="0"/>
@@ -32396,47 +32423,47 @@
     </row>
     <row r="8" spans="1:26" ht="27">
       <c r="A8" s="2" t="s">
-        <v>464</v>
+        <v>474</v>
       </c>
       <c r="B8" s="5" t="str">
         <f>IF($A8="","",IFERROR(VLOOKUP($A8,'02_Конкуренты'!$A$4:$B$203,2,FALSE),"не найдено"))</f>
         <v>Numerous.ai</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>467</v>
+        <v>477</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>468</v>
+        <v>478</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>469</v>
+        <v>479</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>470</v>
+        <v>480</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>471</v>
+        <v>481</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>472</v>
+        <v>482</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>473</v>
+        <v>483</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>474</v>
+        <v>484</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>475</v>
+        <v>485</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>476</v>
+        <v>486</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>477</v>
+        <v>487</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>478</v>
+        <v>488</v>
       </c>
       <c r="O8" s="6">
         <f t="shared" si="0"/>
@@ -32453,47 +32480,47 @@
     </row>
     <row r="9" spans="1:26" ht="40.5">
       <c r="A9" s="2" t="s">
-        <v>505</v>
+        <v>514</v>
       </c>
       <c r="B9" s="5" t="str">
         <f>IF($A9="","",IFERROR(VLOOKUP($A9,'02_Конкуренты'!$A$4:$B$203,2,FALSE),"не найдено"))</f>
         <v>Datarails</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>510</v>
+        <v>519</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>511</v>
+        <v>520</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>512</v>
+        <v>521</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>513</v>
+        <v>522</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>514</v>
+        <v>523</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>515</v>
+        <v>524</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>516</v>
+        <v>525</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>517</v>
+        <v>526</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>518</v>
+        <v>527</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>519</v>
+        <v>528</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>520</v>
+        <v>529</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>521</v>
+        <v>530</v>
       </c>
       <c r="O9" s="6">
         <f t="shared" si="0"/>
@@ -32510,47 +32537,47 @@
     </row>
     <row r="10" spans="1:26" ht="40.5">
       <c r="A10" s="2" t="s">
-        <v>547</v>
+        <v>556</v>
       </c>
       <c r="B10" s="5" t="str">
         <f>IF($A10="","",IFERROR(VLOOKUP($A10,'02_Конкуренты'!$A$4:$B$203,2,FALSE),"не найдено"))</f>
         <v>DataSnipper</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>551</v>
+        <v>560</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>552</v>
+        <v>561</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>553</v>
+        <v>562</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>554</v>
+        <v>563</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>555</v>
+        <v>564</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>556</v>
+        <v>565</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>557</v>
+        <v>566</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>558</v>
+        <v>567</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>559</v>
+        <v>568</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>560</v>
+        <v>569</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>561</v>
+        <v>570</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>562</v>
+        <v>571</v>
       </c>
       <c r="O10" s="6">
         <f t="shared" si="0"/>
@@ -38815,14 +38842,14 @@
     </row>
     <row r="6" spans="1:26" ht="40.5">
       <c r="A6" s="2" t="s">
-        <v>380</v>
+        <v>387</v>
       </c>
       <c r="B6" s="5" t="str">
         <f>IF($A6="","",IFERROR(VLOOKUP($A6,'02_Конкуренты'!$A$4:$B$203,2,FALSE),"не найдено"))</f>
         <v>Operis</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>397</v>
+        <v>404</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>314</v>
@@ -38846,25 +38873,25 @@
         <v>320</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>386</v>
+        <v>393</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>382</v>
+        <v>389</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>398</v>
+        <v>405</v>
       </c>
     </row>
     <row r="7" spans="1:26" ht="27">
       <c r="A7" s="2" t="s">
-        <v>421</v>
+        <v>431</v>
       </c>
       <c r="B7" s="5" t="str">
         <f>IF($A7="","",IFERROR(VLOOKUP($A7,'02_Конкуренты'!$A$4:$B$203,2,FALSE),"не найдено"))</f>
         <v>Shortcut</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>438</v>
+        <v>448</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>314</v>
@@ -38888,25 +38915,25 @@
         <v>320</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>427</v>
+        <v>437</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>423</v>
+        <v>433</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>398</v>
+        <v>405</v>
       </c>
     </row>
     <row r="8" spans="1:26" ht="27">
       <c r="A8" s="2" t="s">
-        <v>464</v>
+        <v>474</v>
       </c>
       <c r="B8" s="5" t="str">
         <f>IF($A8="","",IFERROR(VLOOKUP($A8,'02_Конкуренты'!$A$4:$B$203,2,FALSE),"не найдено"))</f>
         <v>Numerous.ai</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>479</v>
+        <v>489</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>314</v>
@@ -38930,10 +38957,10 @@
         <v>320</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>468</v>
+        <v>478</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>466</v>
+        <v>476</v>
       </c>
       <c r="M8" s="2" t="s">
         <v>321</v>
@@ -38941,14 +38968,14 @@
     </row>
     <row r="9" spans="1:26" ht="40.5">
       <c r="A9" s="2" t="s">
-        <v>505</v>
+        <v>514</v>
       </c>
       <c r="B9" s="5" t="str">
         <f>IF($A9="","",IFERROR(VLOOKUP($A9,'02_Конкуренты'!$A$4:$B$203,2,FALSE),"не найдено"))</f>
         <v>Datarails</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>522</v>
+        <v>531</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>314</v>
@@ -38972,25 +38999,25 @@
         <v>320</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>511</v>
+        <v>520</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>507</v>
+        <v>516</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>398</v>
+        <v>405</v>
       </c>
     </row>
     <row r="10" spans="1:26" ht="40.5">
       <c r="A10" s="2" t="s">
-        <v>547</v>
+        <v>556</v>
       </c>
       <c r="B10" s="5" t="str">
         <f>IF($A10="","",IFERROR(VLOOKUP($A10,'02_Конкуренты'!$A$4:$B$203,2,FALSE),"не найдено"))</f>
         <v>DataSnipper</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>563</v>
+        <v>572</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>314</v>
@@ -39014,13 +39041,13 @@
         <v>320</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>552</v>
+        <v>561</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>549</v>
+        <v>558</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>398</v>
+        <v>405</v>
       </c>
     </row>
     <row r="11" spans="1:26">
@@ -42665,7 +42692,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="5" spans="1:26">
+    <row r="5" spans="1:26" ht="27">
       <c r="A5" s="2" t="s">
         <v>351</v>
       </c>
@@ -42677,115 +42704,115 @@
         <v>54</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>324</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>54</v>
+        <v>371</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>364</v>
+        <v>373</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>364</v>
+        <v>374</v>
       </c>
       <c r="L5" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M5" s="2">
         <v>2</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>368</v>
+        <v>375</v>
       </c>
     </row>
     <row r="6" spans="1:26" ht="27">
       <c r="A6" s="2" t="s">
-        <v>380</v>
+        <v>387</v>
       </c>
       <c r="B6" s="5" t="str">
         <f>IF($A6="","",IFERROR(VLOOKUP($A6,'02_Конкуренты'!$A$4:$B$203,2,FALSE),"не найдено"))</f>
         <v>Operis</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>399</v>
+        <v>406</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>364</v>
+        <v>407</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>324</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>324</v>
+        <v>408</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>400</v>
+        <v>409</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>401</v>
+        <v>410</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>364</v>
+        <v>411</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>402</v>
+        <v>412</v>
       </c>
       <c r="K6" s="2" t="s">
         <v>330</v>
       </c>
       <c r="L6" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M6" s="2">
         <v>2</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>403</v>
+        <v>413</v>
       </c>
     </row>
     <row r="7" spans="1:26" ht="27">
       <c r="A7" s="2" t="s">
-        <v>421</v>
+        <v>431</v>
       </c>
       <c r="B7" s="5" t="str">
         <f>IF($A7="","",IFERROR(VLOOKUP($A7,'02_Конкуренты'!$A$4:$B$203,2,FALSE),"не найдено"))</f>
         <v>Shortcut</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>439</v>
+        <v>449</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>440</v>
+        <v>450</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>441</v>
+        <v>451</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>442</v>
+        <v>452</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>443</v>
+        <v>453</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>444</v>
+        <v>454</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>445</v>
+        <v>455</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>446</v>
+        <v>456</v>
       </c>
       <c r="K7" s="2" t="s">
         <v>330</v>
@@ -42797,12 +42824,12 @@
         <v>4</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>447</v>
+        <v>457</v>
       </c>
     </row>
     <row r="8" spans="1:26" ht="27">
       <c r="A8" s="2" t="s">
-        <v>464</v>
+        <v>474</v>
       </c>
       <c r="B8" s="5" t="str">
         <f>IF($A8="","",IFERROR(VLOOKUP($A8,'02_Конкуренты'!$A$4:$B$203,2,FALSE),"не найдено"))</f>
@@ -42812,28 +42839,28 @@
         <v>16</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>480</v>
+        <v>490</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>324</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>481</v>
+        <v>491</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>482</v>
+        <v>492</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>483</v>
+        <v>493</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>484</v>
+        <v>494</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>485</v>
+        <v>412</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>486</v>
+        <v>495</v>
       </c>
       <c r="L8" s="2">
         <v>5</v>
@@ -42842,40 +42869,40 @@
         <v>2</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>487</v>
+        <v>496</v>
       </c>
     </row>
     <row r="9" spans="1:26">
       <c r="A9" s="2" t="s">
-        <v>505</v>
+        <v>514</v>
       </c>
       <c r="B9" s="5" t="str">
         <f>IF($A9="","",IFERROR(VLOOKUP($A9,'02_Конкуренты'!$A$4:$B$203,2,FALSE),"не найдено"))</f>
         <v>Datarails</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>523</v>
+        <v>532</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>524</v>
+        <v>533</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>324</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>525</v>
+        <v>534</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>526</v>
+        <v>535</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>527</v>
+        <v>536</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>528</v>
+        <v>537</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>485</v>
+        <v>412</v>
       </c>
       <c r="K9" s="2" t="s">
         <v>330</v>
@@ -42887,19 +42914,19 @@
         <v>3</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>529</v>
+        <v>538</v>
       </c>
     </row>
     <row r="10" spans="1:26" ht="27">
       <c r="A10" s="2" t="s">
-        <v>547</v>
+        <v>556</v>
       </c>
       <c r="B10" s="5" t="str">
         <f>IF($A10="","",IFERROR(VLOOKUP($A10,'02_Конкуренты'!$A$4:$B$203,2,FALSE),"не найдено"))</f>
         <v>DataSnipper</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>564</v>
+        <v>573</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>364</v>
@@ -42908,10 +42935,10 @@
         <v>324</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>525</v>
+        <v>534</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>528</v>
+        <v>537</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>54</v>
@@ -42920,7 +42947,7 @@
         <v>364</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>485</v>
+        <v>412</v>
       </c>
       <c r="K10" s="2" t="s">
         <v>330</v>
@@ -42932,7 +42959,7 @@
         <v>2</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>565</v>
+        <v>574</v>
       </c>
     </row>
     <row r="11" spans="1:26">
@@ -46798,19 +46825,19 @@
         <v>Arixcel</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>369</v>
+        <v>376</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>370</v>
+        <v>377</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>17</v>
@@ -46831,43 +46858,43 @@
         <v>2</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>374</v>
+        <v>381</v>
       </c>
     </row>
     <row r="6" spans="1:26">
       <c r="A6" s="2" t="s">
-        <v>380</v>
+        <v>387</v>
       </c>
       <c r="B6" s="5" t="str">
         <f>IF($A6="","",IFERROR(VLOOKUP($A6,'02_Конкуренты'!$A$4:$B$203,2,FALSE),"не найдено"))</f>
         <v>Operis</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>404</v>
+        <v>414</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>405</v>
+        <v>415</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>406</v>
+        <v>416</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>407</v>
+        <v>417</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>408</v>
+        <v>418</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>409</v>
+        <v>419</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>410</v>
+        <v>420</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>324</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>411</v>
+        <v>421</v>
       </c>
       <c r="L6" s="2">
         <v>4</v>
@@ -46876,31 +46903,31 @@
         <v>2</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>412</v>
+        <v>422</v>
       </c>
     </row>
     <row r="7" spans="1:26" ht="27">
       <c r="A7" s="2" t="s">
-        <v>421</v>
+        <v>431</v>
       </c>
       <c r="B7" s="5" t="str">
         <f>IF($A7="","",IFERROR(VLOOKUP($A7,'02_Конкуренты'!$A$4:$B$203,2,FALSE),"не найдено"))</f>
         <v>Shortcut</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>369</v>
+        <v>376</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>448</v>
+        <v>458</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>406</v>
+        <v>416</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>449</v>
+        <v>459</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>450</v>
+        <v>460</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>17</v>
@@ -46909,10 +46936,10 @@
         <v>43</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>451</v>
+        <v>461</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>452</v>
+        <v>462</v>
       </c>
       <c r="L7" s="2">
         <v>2</v>
@@ -46921,43 +46948,43 @@
         <v>5</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>453</v>
+        <v>463</v>
       </c>
     </row>
     <row r="8" spans="1:26" ht="27">
       <c r="A8" s="2" t="s">
-        <v>464</v>
+        <v>474</v>
       </c>
       <c r="B8" s="5" t="str">
         <f>IF($A8="","",IFERROR(VLOOKUP($A8,'02_Конкуренты'!$A$4:$B$203,2,FALSE),"не найдено"))</f>
         <v>Numerous.ai</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>488</v>
+        <v>497</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>489</v>
+        <v>498</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>490</v>
+        <v>499</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>491</v>
+        <v>500</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>492</v>
+        <v>501</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>17</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>493</v>
+        <v>502</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>494</v>
+        <v>503</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>495</v>
+        <v>504</v>
       </c>
       <c r="L8" s="2">
         <v>2</v>
@@ -46966,43 +46993,43 @@
         <v>4</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>496</v>
+        <v>505</v>
       </c>
     </row>
     <row r="9" spans="1:26" ht="27">
       <c r="A9" s="2" t="s">
-        <v>505</v>
+        <v>514</v>
       </c>
       <c r="B9" s="5" t="str">
         <f>IF($A9="","",IFERROR(VLOOKUP($A9,'02_Конкуренты'!$A$4:$B$203,2,FALSE),"не найдено"))</f>
         <v>Datarails</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>530</v>
+        <v>539</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>531</v>
+        <v>540</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>406</v>
+        <v>416</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>532</v>
+        <v>541</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>533</v>
+        <v>542</v>
       </c>
       <c r="H9" s="2" t="s">
+        <v>543</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>544</v>
+      </c>
+      <c r="J9" s="2" t="s">
         <v>534</v>
       </c>
-      <c r="I9" s="2" t="s">
-        <v>535</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>525</v>
-      </c>
       <c r="K9" s="2" t="s">
-        <v>536</v>
+        <v>545</v>
       </c>
       <c r="L9" s="2">
         <v>4</v>
@@ -47011,43 +47038,43 @@
         <v>4</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>537</v>
+        <v>546</v>
       </c>
     </row>
     <row r="10" spans="1:26" ht="27">
       <c r="A10" s="2" t="s">
-        <v>547</v>
+        <v>556</v>
       </c>
       <c r="B10" s="5" t="str">
         <f>IF($A10="","",IFERROR(VLOOKUP($A10,'02_Конкуренты'!$A$4:$B$203,2,FALSE),"не найдено"))</f>
         <v>DataSnipper</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>566</v>
+        <v>575</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>567</v>
+        <v>576</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>406</v>
+        <v>416</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>568</v>
+        <v>577</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>533</v>
+        <v>542</v>
       </c>
       <c r="H10" s="2" t="s">
+        <v>543</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>544</v>
+      </c>
+      <c r="J10" s="2" t="s">
         <v>534</v>
       </c>
-      <c r="I10" s="2" t="s">
-        <v>535</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>525</v>
-      </c>
       <c r="K10" s="2" t="s">
-        <v>569</v>
+        <v>578</v>
       </c>
       <c r="L10" s="2">
         <v>4</v>
@@ -47056,7 +47083,7 @@
         <v>4</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>570</v>
+        <v>579</v>
       </c>
     </row>
     <row r="11" spans="1:26">
@@ -50923,13 +50950,13 @@
         <v>Arixcel</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>375</v>
+        <v>382</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>363</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>376</v>
+        <v>383</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>364</v>
@@ -50941,10 +50968,10 @@
         <v>364</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>370</v>
+        <v>377</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="K5" s="2">
         <v>2</v>
@@ -50953,43 +50980,43 @@
         <v>2</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>378</v>
+        <v>385</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>379</v>
+        <v>386</v>
       </c>
     </row>
     <row r="6" spans="1:26">
       <c r="A6" s="2" t="s">
-        <v>380</v>
+        <v>387</v>
       </c>
       <c r="B6" s="5" t="str">
         <f>IF($A6="","",IFERROR(VLOOKUP($A6,'02_Конкуренты'!$A$4:$B$203,2,FALSE),"не найдено"))</f>
         <v>Operis</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>413</v>
+        <v>423</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>414</v>
+        <v>424</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>416</v>
+        <v>426</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>345</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>417</v>
+        <v>427</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>418</v>
+        <v>428</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>394</v>
+        <v>401</v>
       </c>
       <c r="K6" s="2">
         <v>2</v>
@@ -50998,43 +51025,43 @@
         <v>4</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>419</v>
+        <v>429</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>420</v>
+        <v>430</v>
       </c>
     </row>
     <row r="7" spans="1:26" ht="27">
       <c r="A7" s="2" t="s">
-        <v>421</v>
+        <v>431</v>
       </c>
       <c r="B7" s="5" t="str">
         <f>IF($A7="","",IFERROR(VLOOKUP($A7,'02_Конкуренты'!$A$4:$B$203,2,FALSE),"не найдено"))</f>
         <v>Shortcut</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>454</v>
+        <v>464</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>455</v>
+        <v>465</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>456</v>
+        <v>466</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>457</v>
+        <v>467</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>458</v>
+        <v>468</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>459</v>
+        <v>469</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>460</v>
+        <v>470</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>461</v>
+        <v>471</v>
       </c>
       <c r="K7" s="2">
         <v>4</v>
@@ -51043,43 +51070,43 @@
         <v>3</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>462</v>
+        <v>472</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>463</v>
+        <v>473</v>
       </c>
     </row>
     <row r="8" spans="1:26">
       <c r="A8" s="2" t="s">
-        <v>464</v>
+        <v>474</v>
       </c>
       <c r="B8" s="5" t="str">
         <f>IF($A8="","",IFERROR(VLOOKUP($A8,'02_Конкуренты'!$A$4:$B$203,2,FALSE),"не найдено"))</f>
         <v>Numerous.ai</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>497</v>
+        <v>506</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>498</v>
+        <v>507</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>499</v>
+        <v>508</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>500</v>
+        <v>509</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>475</v>
+        <v>485</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>501</v>
+        <v>510</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>502</v>
+        <v>511</v>
       </c>
       <c r="K8" s="2">
         <v>4</v>
@@ -51088,40 +51115,40 @@
         <v>1</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>503</v>
+        <v>512</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>504</v>
+        <v>513</v>
       </c>
     </row>
     <row r="9" spans="1:26">
       <c r="A9" s="2" t="s">
-        <v>505</v>
+        <v>514</v>
       </c>
       <c r="B9" s="5" t="str">
         <f>IF($A9="","",IFERROR(VLOOKUP($A9,'02_Конкуренты'!$A$4:$B$203,2,FALSE),"не найдено"))</f>
         <v>Datarails</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>538</v>
+        <v>547</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>539</v>
+        <v>548</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>540</v>
+        <v>549</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>541</v>
+        <v>550</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>542</v>
+        <v>551</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>543</v>
+        <v>552</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>544</v>
+        <v>553</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>348</v>
@@ -51133,43 +51160,43 @@
         <v>4</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>545</v>
+        <v>554</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>546</v>
+        <v>555</v>
       </c>
     </row>
     <row r="10" spans="1:26" ht="27">
       <c r="A10" s="2" t="s">
-        <v>547</v>
+        <v>556</v>
       </c>
       <c r="B10" s="5" t="str">
         <f>IF($A10="","",IFERROR(VLOOKUP($A10,'02_Конкуренты'!$A$4:$B$203,2,FALSE),"не найдено"))</f>
         <v>DataSnipper</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>571</v>
+        <v>580</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>572</v>
+        <v>581</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>573</v>
+        <v>582</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>574</v>
+        <v>583</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>575</v>
+        <v>584</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>576</v>
+        <v>585</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>577</v>
+        <v>586</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>578</v>
+        <v>587</v>
       </c>
       <c r="K10" s="2">
         <v>3</v>
@@ -51178,10 +51205,10 @@
         <v>4</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>579</v>
+        <v>588</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>580</v>
+        <v>589</v>
       </c>
     </row>
     <row r="11" spans="1:26">

--- a/ЛР5_Анализ_конкурентов/Excel/ЛР5_3_бизнес_модели_конкурентов_TableMind.xlsx
+++ b/ЛР5_Анализ_конкурентов/Excel/ЛР5_3_бизнес_модели_конкурентов_TableMind.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TableMind_EB\.claude\worktrees\handoff-continuation-57ce20\ЛР5_Анализ_конкурентов\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{512A1526-1D99-4063-9944-736D77BA1587}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEEA5FFA-02E1-474C-B461-29F41E98DE1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="368" yWindow="368" windowWidth="12022" windowHeight="10972" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2205" yWindow="458" windowWidth="12022" windowHeight="10972" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="13_Справочники" sheetId="1" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1073" uniqueCount="694">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1217" uniqueCount="764">
   <si>
     <t>Справочники для раскрывающихся списков</t>
   </si>
@@ -1996,6 +1996,216 @@
   </si>
   <si>
     <t>Присутствует в магазине надстроек</t>
+  </si>
+  <si>
+    <t>F017</t>
+  </si>
+  <si>
+    <t>Безопасность</t>
+  </si>
+  <si>
+    <t>https://www.datasnipper.com/security</t>
+  </si>
+  <si>
+    <t>SOC 2 Type II, Azure, AES-256, TLS 1.2+, хранение до 24 часов, обучение на данных клиентов не ведется, GDPR и AI Act</t>
+  </si>
+  <si>
+    <t>Самый подробный профиль безопасности среди специализированных игроков</t>
+  </si>
+  <si>
+    <t>F018</t>
+  </si>
+  <si>
+    <t>https://www.datasnipper.com/pricing</t>
+  </si>
+  <si>
+    <t>Start, Accelerate, Elevate без сумм; Book demo и Contact sales</t>
+  </si>
+  <si>
+    <t>Цена по запросу, вход через демо</t>
+  </si>
+  <si>
+    <t>F019</t>
+  </si>
+  <si>
+    <t>https://knowledge.datasnipper.com/en/collections/1449483-integrations</t>
+  </si>
+  <si>
+    <t>SharePoint, OneDrive, Box, Dropbox, SAP Concur, QuickBooks, Suralink, Azure</t>
+  </si>
+  <si>
+    <t>Интеграции документов аудита, не проверки формул</t>
+  </si>
+  <si>
+    <t>F020</t>
+  </si>
+  <si>
+    <t>Отзывы Capterra</t>
+  </si>
+  <si>
+    <t>https://www.capterra.com/p/10002513/DataSnipper/</t>
+  </si>
+  <si>
+    <t>4,7 из 5, 131 отзыв, пробной версии нет</t>
+  </si>
+  <si>
+    <t>Сильный репутационный профиль</t>
+  </si>
+  <si>
+    <t>F021</t>
+  </si>
+  <si>
+    <t>https://datarails.com/pricing/</t>
+  </si>
+  <si>
+    <t>Professional, Premium, Expert без сумм; Request Quote, пробного периода нет</t>
+  </si>
+  <si>
+    <t>F022</t>
+  </si>
+  <si>
+    <t>Центр доверия</t>
+  </si>
+  <si>
+    <t>https://trust.datarails.com/overview</t>
+  </si>
+  <si>
+    <t>SOC 2 Type II, SOC 1, политика информационной безопасности, тест на проникновение; отчеты по запросу</t>
+  </si>
+  <si>
+    <t>Самый полный профиль доверия</t>
+  </si>
+  <si>
+    <t>F023</t>
+  </si>
+  <si>
+    <t>https://datarails.com/integrations/</t>
+  </si>
+  <si>
+    <t>более 200 интеграций в списке (ERP, CRM, хранилища); на главной заявлено более 600</t>
+  </si>
+  <si>
+    <t>Интеграции - барьер переключения</t>
+  </si>
+  <si>
+    <t>F024</t>
+  </si>
+  <si>
+    <t>https://www.capterra.com/p/177451/DataRails/</t>
+  </si>
+  <si>
+    <t>4,7 из 5, 245 отзывов</t>
+  </si>
+  <si>
+    <t>F025</t>
+  </si>
+  <si>
+    <t>Лицензирование</t>
+  </si>
+  <si>
+    <t>https://www.arixcel.com/explorer/download</t>
+  </si>
+  <si>
+    <t>2,75 GBP за пользователя в месяц, лицензия 12-36 месяцев, только Windows, пробный режим</t>
+  </si>
+  <si>
+    <t>Цена опубликована, лестницы тарифов нет</t>
+  </si>
+  <si>
+    <t>F026</t>
+  </si>
+  <si>
+    <t>Цены OAK</t>
+  </si>
+  <si>
+    <t>https://www.operisanalysiskit.com/oak-price/</t>
+  </si>
+  <si>
+    <t>подписка 311,66 GBP в год, более 30 инструментов, Try OAK и Buy now</t>
+  </si>
+  <si>
+    <t>Единичная цена, продажа без консультанта</t>
+  </si>
+  <si>
+    <t>F027</t>
+  </si>
+  <si>
+    <t>https://shortcut.ai/privacy</t>
+  </si>
+  <si>
+    <t>SOC 2 Type II, AES-256, TLS 1.3, нулевое хранение у провайдеров, SAML, ролевой доступ</t>
+  </si>
+  <si>
+    <t>Безопасность раскрыта в центре приватности</t>
+  </si>
+  <si>
+    <t>F028</t>
+  </si>
+  <si>
+    <t>Цены и регистрация</t>
+  </si>
+  <si>
+    <t>https://numerous.ai/</t>
+  </si>
+  <si>
+    <t>7 дней бесплатно, оплата за год, 10 USD в месяц, лимит 500 тыс. символов</t>
+  </si>
+  <si>
+    <t>Путь от пробы к подписке без продавца</t>
+  </si>
+  <si>
+    <t>F029</t>
+  </si>
+  <si>
+    <t>Подвал сайта</t>
+  </si>
+  <si>
+    <t>только политика конфиденциальности и условия, заявлений о безопасности нет</t>
+  </si>
+  <si>
+    <t>Безопасность не раскрыта</t>
+  </si>
+  <si>
+    <t>F030</t>
+  </si>
+  <si>
+    <t>Отзывы Trustpilot</t>
+  </si>
+  <si>
+    <t>https://www.trustpilot.com/review/numerous.ai</t>
+  </si>
+  <si>
+    <t>2,5 из 5, 5 отзывов, жалобы на автосписание после пробного периода</t>
+  </si>
+  <si>
+    <t>Риск политики пробного периода</t>
+  </si>
+  <si>
+    <t>F031</t>
+  </si>
+  <si>
+    <t>Пробный период</t>
+  </si>
+  <si>
+    <t>https://www.perfectxl.com/products/perfectxl-formula-inspector/free-trial-vdependents/</t>
+  </si>
+  <si>
+    <t>30 дней без карты и автопродления, Excel 2016 и новее</t>
+  </si>
+  <si>
+    <t>Бесплатный вход есть</t>
+  </si>
+  <si>
+    <t>F032</t>
+  </si>
+  <si>
+    <t>Правовые страницы</t>
+  </si>
+  <si>
+    <t>https://www.perfectxl.com/legal/privacy-policy/</t>
+  </si>
+  <si>
+    <t>политика конфиденциальности, условия, cookie; страницы безопасности нет</t>
   </si>
   <si>
     <t>Надстройка Excel или Excel-интеграция</t>
@@ -2377,19 +2587,19 @@
                   <c:v>Shortcut</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>Datarails</c:v>
+                  <c:v>DataSnipper</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>DataSnipper</c:v>
+                  <c:v>Datarails</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>PerfectXL</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>Numerous.ai</c:v>
+                  <c:v>Operis</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>Operis</c:v>
+                  <c:v>Numerous.ai</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>Arixcel</c:v>
@@ -2404,25 +2614,25 @@
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>4.2621212121212118</c:v>
+                  <c:v>4.2829545454545457</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>4.2363636363636363</c:v>
+                  <c:v>4.207575757575758</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>4.165909090909091</c:v>
+                  <c:v>4.1946969696969694</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>3.9090909090909092</c:v>
+                  <c:v>3.8590909090909089</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>3.581818181818182</c:v>
+                  <c:v>3.4954545454545451</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>3.3704545454545451</c:v>
+                  <c:v>3.4818181818181815</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>3.0045454545454544</c:v>
+                  <c:v>3.0878787878787879</c:v>
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>0</c:v>
@@ -2438,7 +2648,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-C507-44E1-BB60-FBFA8A9F5124}"/>
+              <c16:uniqueId val="{00000000-66FD-40EB-8094-D882604E9355}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3431,7 +3641,7 @@
       </c>
       <c r="O4" s="7">
         <f>IF($A4="","",IFERROR(VLOOKUP($A4,'04_Бизнес_модель'!$A$4:$P$203,16,FALSE),0))</f>
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="P4" s="6">
         <f>IF($A4="","",IFERROR(VLOOKUP($A4,'04_Бизнес_модель'!$A$4:$O$203,15,FALSE),0))</f>
@@ -3439,7 +3649,7 @@
       </c>
       <c r="Q4" s="7">
         <f t="shared" ref="Q4:Q35" si="1">IF($A4="","",$N4*0.6+$O4*0.25+$P4*5*0.15)</f>
-        <v>3.9090909090909092</v>
+        <v>3.8590909090909089</v>
       </c>
     </row>
     <row r="5" spans="1:26">
@@ -3489,7 +3699,7 @@
       </c>
       <c r="O5" s="7">
         <f>IF($A5="","",IFERROR(VLOOKUP($A5,'04_Бизнес_модель'!$A$4:$P$203,16,FALSE),0))</f>
-        <v>4</v>
+        <v>4.333333333333333</v>
       </c>
       <c r="P5" s="6">
         <f>IF($A5="","",IFERROR(VLOOKUP($A5,'04_Бизнес_модель'!$A$4:$O$203,15,FALSE),0))</f>
@@ -3497,7 +3707,7 @@
       </c>
       <c r="Q5" s="7">
         <f t="shared" si="1"/>
-        <v>3.0045454545454544</v>
+        <v>3.0878787878787879</v>
       </c>
     </row>
     <row r="6" spans="1:26">
@@ -3547,7 +3757,7 @@
       </c>
       <c r="O6" s="7">
         <f>IF($A6="","",IFERROR(VLOOKUP($A6,'04_Бизнес_модель'!$A$4:$P$203,16,FALSE),0))</f>
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="P6" s="6">
         <f>IF($A6="","",IFERROR(VLOOKUP($A6,'04_Бизнес_модель'!$A$4:$O$203,15,FALSE),0))</f>
@@ -3555,7 +3765,7 @@
       </c>
       <c r="Q6" s="7">
         <f t="shared" si="1"/>
-        <v>3.3704545454545451</v>
+        <v>3.4954545454545451</v>
       </c>
     </row>
     <row r="7" spans="1:26">
@@ -3605,7 +3815,7 @@
       </c>
       <c r="O7" s="7">
         <f>IF($A7="","",IFERROR(VLOOKUP($A7,'04_Бизнес_модель'!$A$4:$P$203,16,FALSE),0))</f>
-        <v>4.666666666666667</v>
+        <v>4.75</v>
       </c>
       <c r="P7" s="6">
         <f>IF($A7="","",IFERROR(VLOOKUP($A7,'04_Бизнес_модель'!$A$4:$O$203,15,FALSE),0))</f>
@@ -3613,7 +3823,7 @@
       </c>
       <c r="Q7" s="7">
         <f t="shared" si="1"/>
-        <v>4.2621212121212118</v>
+        <v>4.2829545454545457</v>
       </c>
     </row>
     <row r="8" spans="1:26">
@@ -3663,7 +3873,7 @@
       </c>
       <c r="O8" s="7">
         <f>IF($A8="","",IFERROR(VLOOKUP($A8,'04_Бизнес_модель'!$A$4:$P$203,16,FALSE),0))</f>
-        <v>5</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="P8" s="6">
         <f>IF($A8="","",IFERROR(VLOOKUP($A8,'04_Бизнес_модель'!$A$4:$O$203,15,FALSE),0))</f>
@@ -3671,7 +3881,7 @@
       </c>
       <c r="Q8" s="7">
         <f t="shared" si="1"/>
-        <v>3.581818181818182</v>
+        <v>3.4818181818181815</v>
       </c>
     </row>
     <row r="9" spans="1:26">
@@ -3721,7 +3931,7 @@
       </c>
       <c r="O9" s="7">
         <f>IF($A9="","",IFERROR(VLOOKUP($A9,'04_Бизнес_модель'!$A$4:$P$203,16,FALSE),0))</f>
-        <v>5</v>
+        <v>4.833333333333333</v>
       </c>
       <c r="P9" s="6">
         <f>IF($A9="","",IFERROR(VLOOKUP($A9,'04_Бизнес_модель'!$A$4:$O$203,15,FALSE),0))</f>
@@ -3729,7 +3939,7 @@
       </c>
       <c r="Q9" s="7">
         <f t="shared" si="1"/>
-        <v>4.2363636363636363</v>
+        <v>4.1946969696969694</v>
       </c>
     </row>
     <row r="10" spans="1:26">
@@ -3779,7 +3989,7 @@
       </c>
       <c r="O10" s="7">
         <f>IF($A10="","",IFERROR(VLOOKUP($A10,'04_Бизнес_модель'!$A$4:$P$203,16,FALSE),0))</f>
-        <v>4.5</v>
+        <v>4.666666666666667</v>
       </c>
       <c r="P10" s="6">
         <f>IF($A10="","",IFERROR(VLOOKUP($A10,'04_Бизнес_модель'!$A$4:$O$203,15,FALSE),0))</f>
@@ -3787,7 +3997,7 @@
       </c>
       <c r="Q10" s="7">
         <f t="shared" si="1"/>
-        <v>4.165909090909091</v>
+        <v>4.207575757575758</v>
       </c>
     </row>
     <row r="11" spans="1:26">
@@ -10463,13 +10673,13 @@
     </row>
     <row r="4" spans="1:26" ht="27">
       <c r="A4" s="2" t="s">
-        <v>650</v>
+        <v>720</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>155</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>651</v>
+        <v>721</v>
       </c>
       <c r="D4" s="2">
         <v>7</v>
@@ -10487,18 +10697,18 @@
         <v>необходимо включить в минимально приемлемое предложение</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>652</v>
+        <v>722</v>
       </c>
     </row>
     <row r="5" spans="1:26" ht="27">
       <c r="A5" s="2" t="s">
-        <v>653</v>
+        <v>723</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>158</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>654</v>
+        <v>724</v>
       </c>
       <c r="D5" s="2">
         <v>2</v>
@@ -10516,18 +10726,18 @@
         <v>может использоваться как поле позиционирования</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>652</v>
+        <v>722</v>
       </c>
     </row>
     <row r="6" spans="1:26" ht="27">
       <c r="A6" s="2" t="s">
-        <v>655</v>
+        <v>725</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>157</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>656</v>
+        <v>726</v>
       </c>
       <c r="D6" s="2">
         <v>3</v>
@@ -10545,18 +10755,18 @@
         <v>проверить значимость для клиента и вероятность закрепления</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>652</v>
+        <v>722</v>
       </c>
     </row>
     <row r="7" spans="1:26" ht="27">
       <c r="A7" s="2" t="s">
-        <v>657</v>
+        <v>727</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>156</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>658</v>
+        <v>728</v>
       </c>
       <c r="D7" s="2">
         <v>4</v>
@@ -10574,18 +10784,18 @@
         <v>проверить значимость для клиента и вероятность закрепления</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>652</v>
+        <v>722</v>
       </c>
     </row>
     <row r="8" spans="1:26" ht="27">
       <c r="A8" s="2" t="s">
-        <v>659</v>
+        <v>729</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>159</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>660</v>
+        <v>730</v>
       </c>
       <c r="D8" s="2">
         <v>3</v>
@@ -10603,18 +10813,18 @@
         <v>проверить значимость для клиента и вероятность закрепления</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>652</v>
+        <v>722</v>
       </c>
     </row>
     <row r="9" spans="1:26">
       <c r="A9" s="2" t="s">
-        <v>661</v>
+        <v>731</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>154</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>662</v>
+        <v>732</v>
       </c>
       <c r="D9" s="2">
         <v>5</v>
@@ -10632,18 +10842,18 @@
         <v>необходимо включить в минимально приемлемое предложение</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>652</v>
+        <v>722</v>
       </c>
     </row>
     <row r="10" spans="1:26">
       <c r="A10" s="2" t="s">
-        <v>663</v>
+        <v>733</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>158</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>664</v>
+        <v>734</v>
       </c>
       <c r="D10" s="2">
         <v>5</v>
@@ -10661,18 +10871,18 @@
         <v>необходимо включить в минимально приемлемое предложение</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>652</v>
+        <v>722</v>
       </c>
     </row>
     <row r="11" spans="1:26">
       <c r="A11" s="2" t="s">
-        <v>665</v>
+        <v>735</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>157</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>666</v>
+        <v>736</v>
       </c>
       <c r="D11" s="2">
         <v>6</v>
@@ -10690,18 +10900,18 @@
         <v>необходимо включить в минимально приемлемое предложение</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>652</v>
+        <v>722</v>
       </c>
     </row>
     <row r="12" spans="1:26">
       <c r="A12" s="2" t="s">
-        <v>667</v>
+        <v>737</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>155</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>668</v>
+        <v>738</v>
       </c>
       <c r="D12" s="2">
         <v>4</v>
@@ -10719,18 +10929,18 @@
         <v>проверить значимость для клиента и вероятность закрепления</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>652</v>
+        <v>722</v>
       </c>
     </row>
     <row r="13" spans="1:26" ht="27">
       <c r="A13" s="2" t="s">
-        <v>669</v>
+        <v>739</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>155</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>670</v>
+        <v>740</v>
       </c>
       <c r="D13" s="2">
         <v>2</v>
@@ -10748,18 +10958,18 @@
         <v>может использоваться как поле позиционирования</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>652</v>
+        <v>722</v>
       </c>
     </row>
     <row r="14" spans="1:26" ht="27">
       <c r="A14" s="2" t="s">
-        <v>671</v>
+        <v>741</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>158</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>672</v>
+        <v>742</v>
       </c>
       <c r="D14" s="2">
         <v>4</v>
@@ -10777,18 +10987,18 @@
         <v>проверить значимость для клиента и вероятность закрепления</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>652</v>
+        <v>722</v>
       </c>
     </row>
     <row r="15" spans="1:26">
       <c r="A15" s="2" t="s">
-        <v>673</v>
+        <v>743</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>161</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>674</v>
+        <v>744</v>
       </c>
       <c r="D15" s="2">
         <v>4</v>
@@ -10806,7 +11016,7 @@
         <v>проверить значимость для клиента и вероятность закрепления</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>652</v>
+        <v>722</v>
       </c>
     </row>
     <row r="16" spans="1:26">
@@ -14526,16 +14736,16 @@
         <v>PerfectXL</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>675</v>
+        <v>745</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>676</v>
+        <v>746</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>154</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>677</v>
+        <v>747</v>
       </c>
       <c r="G4" s="2">
         <v>4</v>
@@ -14558,7 +14768,7 @@
         <v>умеренное преимущество</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>678</v>
+        <v>748</v>
       </c>
     </row>
     <row r="5" spans="1:26" ht="27">
@@ -14570,7 +14780,7 @@
         <v>PerfectXL</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>679</v>
+        <v>749</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>19</v>
@@ -14579,7 +14789,7 @@
         <v>155</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>680</v>
+        <v>750</v>
       </c>
       <c r="G5" s="2">
         <v>4</v>
@@ -14602,7 +14812,7 @@
         <v>умеренное преимущество</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>678</v>
+        <v>748</v>
       </c>
     </row>
     <row r="6" spans="1:26" ht="27">
@@ -14614,10 +14824,10 @@
         <v>Shortcut</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>681</v>
+        <v>751</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>682</v>
+        <v>752</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>158</v>
@@ -14646,7 +14856,7 @@
         <v>умеренное преимущество</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>678</v>
+        <v>748</v>
       </c>
     </row>
     <row r="7" spans="1:26" ht="27">
@@ -14658,16 +14868,16 @@
         <v>Shortcut</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>683</v>
+        <v>753</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>676</v>
+        <v>746</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>684</v>
+        <v>754</v>
       </c>
       <c r="G7" s="2">
         <v>5</v>
@@ -14690,7 +14900,7 @@
         <v>сильное преимущество</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>678</v>
+        <v>748</v>
       </c>
     </row>
     <row r="8" spans="1:26" ht="27">
@@ -14702,7 +14912,7 @@
         <v>Numerous.ai</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>685</v>
+        <v>755</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>28</v>
@@ -14734,7 +14944,7 @@
         <v>слабое преимущество</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>678</v>
+        <v>748</v>
       </c>
     </row>
     <row r="9" spans="1:26" ht="27">
@@ -14746,16 +14956,16 @@
         <v>Datarails</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>686</v>
+        <v>756</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>687</v>
+        <v>757</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>161</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>688</v>
+        <v>758</v>
       </c>
       <c r="G9" s="2">
         <v>5</v>
@@ -14778,7 +14988,7 @@
         <v>сильное преимущество</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>678</v>
+        <v>748</v>
       </c>
     </row>
     <row r="10" spans="1:26" ht="27">
@@ -14790,16 +15000,16 @@
         <v>DataSnipper</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>689</v>
+        <v>759</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>676</v>
+        <v>746</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>154</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>690</v>
+        <v>760</v>
       </c>
       <c r="G10" s="2">
         <v>5</v>
@@ -14822,7 +15032,7 @@
         <v>сильное преимущество</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>678</v>
+        <v>748</v>
       </c>
     </row>
     <row r="11" spans="1:26" ht="27">
@@ -14834,16 +15044,16 @@
         <v>Operis</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>691</v>
+        <v>761</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>692</v>
+        <v>762</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>154</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>693</v>
+        <v>763</v>
       </c>
       <c r="G11" s="2">
         <v>4</v>
@@ -14866,7 +15076,7 @@
         <v>сильное преимущество</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>678</v>
+        <v>748</v>
       </c>
     </row>
     <row r="12" spans="1:26">
@@ -19627,7 +19837,7 @@
       </c>
       <c r="G6" s="14">
         <f>IFERROR(LARGE('09_Матрица'!$Q$4:$Q$203,ROW(A1)),"")</f>
-        <v>4.2621212121212118</v>
+        <v>4.2829545454545457</v>
       </c>
     </row>
     <row r="7" spans="1:26" ht="15">
@@ -19647,11 +19857,11 @@
       </c>
       <c r="F7" s="2" t="str">
         <f>IFERROR(INDEX('09_Матрица'!$B$4:$B$203,MATCH(LARGE('09_Матрица'!$Q$4:$Q$203,ROW(A2)),'09_Матрица'!$Q$4:$Q$203,0)),"")</f>
-        <v>Datarails</v>
+        <v>DataSnipper</v>
       </c>
       <c r="G7" s="14">
         <f>IFERROR(LARGE('09_Матрица'!$Q$4:$Q$203,ROW(A2)),"")</f>
-        <v>4.2363636363636363</v>
+        <v>4.207575757575758</v>
       </c>
     </row>
     <row r="8" spans="1:26" ht="30">
@@ -19671,11 +19881,11 @@
       </c>
       <c r="F8" s="2" t="str">
         <f>IFERROR(INDEX('09_Матрица'!$B$4:$B$203,MATCH(LARGE('09_Матрица'!$Q$4:$Q$203,ROW(A3)),'09_Матрица'!$Q$4:$Q$203,0)),"")</f>
-        <v>DataSnipper</v>
+        <v>Datarails</v>
       </c>
       <c r="G8" s="14">
         <f>IFERROR(LARGE('09_Матрица'!$Q$4:$Q$203,ROW(A3)),"")</f>
-        <v>4.165909090909091</v>
+        <v>4.1946969696969694</v>
       </c>
     </row>
     <row r="9" spans="1:26" ht="30">
@@ -19684,7 +19894,7 @@
       </c>
       <c r="B9" s="12">
         <f>IFERROR(AVERAGE('04_Бизнес_модель'!$P$4:$P$203),0)</f>
-        <v>4.5238095238095237</v>
+        <v>4.5690476190476188</v>
       </c>
       <c r="C9" s="10" t="s">
         <v>270</v>
@@ -19699,7 +19909,7 @@
       </c>
       <c r="G9" s="14">
         <f>IFERROR(LARGE('09_Матрица'!$Q$4:$Q$203,ROW(A4)),"")</f>
-        <v>3.9090909090909092</v>
+        <v>3.8590909090909089</v>
       </c>
     </row>
     <row r="10" spans="1:26" ht="30">
@@ -19708,7 +19918,7 @@
       </c>
       <c r="B10" s="12">
         <f>IFERROR(AVERAGE('09_Матрица'!$Q$4:$Q$203),0)</f>
-        <v>3.7900432900432901</v>
+        <v>3.8013528138528137</v>
       </c>
       <c r="C10" s="10" t="s">
         <v>272</v>
@@ -19719,11 +19929,11 @@
       </c>
       <c r="F10" s="2" t="str">
         <f>IFERROR(INDEX('09_Матрица'!$B$4:$B$203,MATCH(LARGE('09_Матрица'!$Q$4:$Q$203,ROW(A5)),'09_Матрица'!$Q$4:$Q$203,0)),"")</f>
-        <v>Numerous.ai</v>
+        <v>Operis</v>
       </c>
       <c r="G10" s="14">
         <f>IFERROR(LARGE('09_Матрица'!$Q$4:$Q$203,ROW(A5)),"")</f>
-        <v>3.581818181818182</v>
+        <v>3.4954545454545451</v>
       </c>
     </row>
     <row r="11" spans="1:26" ht="30">
@@ -19743,11 +19953,11 @@
       </c>
       <c r="F11" s="2" t="str">
         <f>IFERROR(INDEX('09_Матрица'!$B$4:$B$203,MATCH(LARGE('09_Матрица'!$Q$4:$Q$203,ROW(A6)),'09_Матрица'!$Q$4:$Q$203,0)),"")</f>
-        <v>Operis</v>
+        <v>Numerous.ai</v>
       </c>
       <c r="G11" s="14">
         <f>IFERROR(LARGE('09_Матрица'!$Q$4:$Q$203,ROW(A6)),"")</f>
-        <v>3.3704545454545451</v>
+        <v>3.4818181818181815</v>
       </c>
     </row>
     <row r="12" spans="1:26">
@@ -19761,7 +19971,7 @@
       </c>
       <c r="G12" s="14">
         <f>IFERROR(LARGE('09_Матрица'!$Q$4:$Q$203,ROW(A7)),"")</f>
-        <v>3.0045454545454544</v>
+        <v>3.0878787878787879</v>
       </c>
     </row>
     <row r="13" spans="1:26">
@@ -23806,277 +24016,629 @@
         <v>649</v>
       </c>
     </row>
-    <row r="20" spans="1:12">
-      <c r="A20" s="2"/>
-      <c r="B20" s="2"/>
+    <row r="20" spans="1:12" ht="40.5">
+      <c r="A20" s="2" t="s">
+        <v>650</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>556</v>
+      </c>
       <c r="C20" s="5" t="str">
         <f>IF($B20="","",IFERROR(VLOOKUP($B20,'02_Конкуренты'!$A$4:$B$203,2,FALSE),"не найдено"))</f>
-        <v/>
-      </c>
-      <c r="D20" s="2"/>
-      <c r="E20" s="2"/>
-      <c r="F20" s="2"/>
-      <c r="G20" s="2"/>
-      <c r="H20" s="2"/>
-      <c r="I20" s="2"/>
-      <c r="J20" s="4"/>
-      <c r="K20" s="2"/>
-      <c r="L20" s="2"/>
-    </row>
-    <row r="21" spans="1:12">
-      <c r="A21" s="2"/>
-      <c r="B21" s="2"/>
+        <v>DataSnipper</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>652</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>653</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="I20" s="2">
+        <v>5</v>
+      </c>
+      <c r="J20" s="4">
+        <v>46298</v>
+      </c>
+      <c r="K20" s="2" t="s">
+        <v>593</v>
+      </c>
+      <c r="L20" s="2" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" ht="27">
+      <c r="A21" s="2" t="s">
+        <v>655</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>556</v>
+      </c>
       <c r="C21" s="5" t="str">
         <f>IF($B21="","",IFERROR(VLOOKUP($B21,'02_Конкуренты'!$A$4:$B$203,2,FALSE),"не найдено"))</f>
-        <v/>
-      </c>
-      <c r="D21" s="2"/>
-      <c r="E21" s="2"/>
-      <c r="F21" s="2"/>
-      <c r="G21" s="2"/>
-      <c r="H21" s="2"/>
-      <c r="I21" s="2"/>
-      <c r="J21" s="4"/>
-      <c r="K21" s="2"/>
-      <c r="L21" s="2"/>
-    </row>
-    <row r="22" spans="1:12">
-      <c r="A22" s="2"/>
-      <c r="B22" s="2"/>
+        <v>DataSnipper</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>596</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>656</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>596</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>657</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="I21" s="2">
+        <v>5</v>
+      </c>
+      <c r="J21" s="4">
+        <v>46298</v>
+      </c>
+      <c r="K21" s="2" t="s">
+        <v>593</v>
+      </c>
+      <c r="L21" s="2" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" ht="27">
+      <c r="A22" s="2" t="s">
+        <v>659</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>556</v>
+      </c>
       <c r="C22" s="5" t="str">
         <f>IF($B22="","",IFERROR(VLOOKUP($B22,'02_Конкуренты'!$A$4:$B$203,2,FALSE),"не найдено"))</f>
-        <v/>
-      </c>
-      <c r="D22" s="2"/>
-      <c r="E22" s="2"/>
-      <c r="F22" s="2"/>
-      <c r="G22" s="2"/>
-      <c r="H22" s="2"/>
-      <c r="I22" s="2"/>
-      <c r="J22" s="4"/>
-      <c r="K22" s="2"/>
-      <c r="L22" s="2"/>
-    </row>
-    <row r="23" spans="1:12">
-      <c r="A23" s="2"/>
-      <c r="B23" s="2"/>
+        <v>DataSnipper</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>660</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>661</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="I22" s="2">
+        <v>4</v>
+      </c>
+      <c r="J22" s="4">
+        <v>46298</v>
+      </c>
+      <c r="K22" s="2" t="s">
+        <v>593</v>
+      </c>
+      <c r="L22" s="2" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" ht="27">
+      <c r="A23" s="2" t="s">
+        <v>663</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>556</v>
+      </c>
       <c r="C23" s="5" t="str">
         <f>IF($B23="","",IFERROR(VLOOKUP($B23,'02_Конкуренты'!$A$4:$B$203,2,FALSE),"не найдено"))</f>
-        <v/>
-      </c>
-      <c r="D23" s="2"/>
-      <c r="E23" s="2"/>
-      <c r="F23" s="2"/>
-      <c r="G23" s="2"/>
-      <c r="H23" s="2"/>
-      <c r="I23" s="2"/>
-      <c r="J23" s="4"/>
-      <c r="K23" s="2"/>
-      <c r="L23" s="2"/>
-    </row>
-    <row r="24" spans="1:12">
-      <c r="A24" s="2"/>
-      <c r="B24" s="2"/>
+        <v>DataSnipper</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>664</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>665</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>664</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>666</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="I23" s="2">
+        <v>5</v>
+      </c>
+      <c r="J23" s="4">
+        <v>46298</v>
+      </c>
+      <c r="K23" s="2" t="s">
+        <v>593</v>
+      </c>
+      <c r="L23" s="2" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" ht="27">
+      <c r="A24" s="2" t="s">
+        <v>668</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>514</v>
+      </c>
       <c r="C24" s="5" t="str">
         <f>IF($B24="","",IFERROR(VLOOKUP($B24,'02_Конкуренты'!$A$4:$B$203,2,FALSE),"не найдено"))</f>
-        <v/>
-      </c>
-      <c r="D24" s="2"/>
-      <c r="E24" s="2"/>
-      <c r="F24" s="2"/>
-      <c r="G24" s="2"/>
-      <c r="H24" s="2"/>
-      <c r="I24" s="2"/>
-      <c r="J24" s="4"/>
-      <c r="K24" s="2"/>
-      <c r="L24" s="2"/>
-    </row>
-    <row r="25" spans="1:12">
-      <c r="A25" s="2"/>
-      <c r="B25" s="2"/>
+        <v>Datarails</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>596</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>669</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>596</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>670</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="I24" s="2">
+        <v>5</v>
+      </c>
+      <c r="J24" s="4">
+        <v>46298</v>
+      </c>
+      <c r="K24" s="2" t="s">
+        <v>593</v>
+      </c>
+      <c r="L24" s="2" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" ht="40.5">
+      <c r="A25" s="2" t="s">
+        <v>671</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>514</v>
+      </c>
       <c r="C25" s="5" t="str">
         <f>IF($B25="","",IFERROR(VLOOKUP($B25,'02_Конкуренты'!$A$4:$B$203,2,FALSE),"не найдено"))</f>
-        <v/>
-      </c>
-      <c r="D25" s="2"/>
-      <c r="E25" s="2"/>
-      <c r="F25" s="2"/>
-      <c r="G25" s="2"/>
-      <c r="H25" s="2"/>
-      <c r="I25" s="2"/>
-      <c r="J25" s="4"/>
-      <c r="K25" s="2"/>
-      <c r="L25" s="2"/>
-    </row>
-    <row r="26" spans="1:12">
-      <c r="A26" s="2"/>
-      <c r="B26" s="2"/>
+        <v>Datarails</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>672</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>673</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>672</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>674</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="I25" s="2">
+        <v>5</v>
+      </c>
+      <c r="J25" s="4">
+        <v>46298</v>
+      </c>
+      <c r="K25" s="2" t="s">
+        <v>593</v>
+      </c>
+      <c r="L25" s="2" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" ht="27">
+      <c r="A26" s="2" t="s">
+        <v>676</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>514</v>
+      </c>
       <c r="C26" s="5" t="str">
         <f>IF($B26="","",IFERROR(VLOOKUP($B26,'02_Конкуренты'!$A$4:$B$203,2,FALSE),"не найдено"))</f>
-        <v/>
-      </c>
-      <c r="D26" s="2"/>
-      <c r="E26" s="2"/>
-      <c r="F26" s="2"/>
-      <c r="G26" s="2"/>
-      <c r="H26" s="2"/>
-      <c r="I26" s="2"/>
-      <c r="J26" s="4"/>
-      <c r="K26" s="2"/>
-      <c r="L26" s="2"/>
-    </row>
-    <row r="27" spans="1:12">
-      <c r="A27" s="2"/>
-      <c r="B27" s="2"/>
+        <v>Datarails</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>677</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>678</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="I26" s="2">
+        <v>4</v>
+      </c>
+      <c r="J26" s="4">
+        <v>46298</v>
+      </c>
+      <c r="K26" s="2" t="s">
+        <v>593</v>
+      </c>
+      <c r="L26" s="2" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" ht="27">
+      <c r="A27" s="2" t="s">
+        <v>680</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>514</v>
+      </c>
       <c r="C27" s="5" t="str">
         <f>IF($B27="","",IFERROR(VLOOKUP($B27,'02_Конкуренты'!$A$4:$B$203,2,FALSE),"не найдено"))</f>
-        <v/>
-      </c>
-      <c r="D27" s="2"/>
-      <c r="E27" s="2"/>
-      <c r="F27" s="2"/>
-      <c r="G27" s="2"/>
-      <c r="H27" s="2"/>
-      <c r="I27" s="2"/>
-      <c r="J27" s="4"/>
-      <c r="K27" s="2"/>
-      <c r="L27" s="2"/>
-    </row>
-    <row r="28" spans="1:12">
-      <c r="A28" s="2"/>
-      <c r="B28" s="2"/>
+        <v>Datarails</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>664</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>681</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>664</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>682</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="I27" s="2">
+        <v>5</v>
+      </c>
+      <c r="J27" s="4">
+        <v>46298</v>
+      </c>
+      <c r="K27" s="2" t="s">
+        <v>593</v>
+      </c>
+      <c r="L27" s="2" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" ht="40.5">
+      <c r="A28" s="2" t="s">
+        <v>683</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>351</v>
+      </c>
       <c r="C28" s="5" t="str">
         <f>IF($B28="","",IFERROR(VLOOKUP($B28,'02_Конкуренты'!$A$4:$B$203,2,FALSE),"не найдено"))</f>
-        <v/>
-      </c>
-      <c r="D28" s="2"/>
-      <c r="E28" s="2"/>
-      <c r="F28" s="2"/>
-      <c r="G28" s="2"/>
-      <c r="H28" s="2"/>
-      <c r="I28" s="2"/>
-      <c r="J28" s="4"/>
-      <c r="K28" s="2"/>
-      <c r="L28" s="2"/>
-    </row>
-    <row r="29" spans="1:12">
-      <c r="A29" s="2"/>
-      <c r="B29" s="2"/>
+        <v>Arixcel</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>684</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>685</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>684</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>686</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="I28" s="2">
+        <v>5</v>
+      </c>
+      <c r="J28" s="4">
+        <v>46298</v>
+      </c>
+      <c r="K28" s="2" t="s">
+        <v>593</v>
+      </c>
+      <c r="L28" s="2" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" ht="27">
+      <c r="A29" s="2" t="s">
+        <v>688</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>387</v>
+      </c>
       <c r="C29" s="5" t="str">
         <f>IF($B29="","",IFERROR(VLOOKUP($B29,'02_Конкуренты'!$A$4:$B$203,2,FALSE),"не найдено"))</f>
-        <v/>
-      </c>
-      <c r="D29" s="2"/>
-      <c r="E29" s="2"/>
-      <c r="F29" s="2"/>
-      <c r="G29" s="2"/>
-      <c r="H29" s="2"/>
-      <c r="I29" s="2"/>
-      <c r="J29" s="4"/>
-      <c r="K29" s="2"/>
-      <c r="L29" s="2"/>
-    </row>
-    <row r="30" spans="1:12">
-      <c r="A30" s="2"/>
-      <c r="B30" s="2"/>
+        <v>Operis</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>689</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>690</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>689</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>691</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="I29" s="2">
+        <v>5</v>
+      </c>
+      <c r="J29" s="4">
+        <v>46298</v>
+      </c>
+      <c r="K29" s="2" t="s">
+        <v>593</v>
+      </c>
+      <c r="L29" s="2" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" ht="27">
+      <c r="A30" s="2" t="s">
+        <v>693</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>431</v>
+      </c>
       <c r="C30" s="5" t="str">
         <f>IF($B30="","",IFERROR(VLOOKUP($B30,'02_Конкуренты'!$A$4:$B$203,2,FALSE),"не найдено"))</f>
-        <v/>
-      </c>
-      <c r="D30" s="2"/>
-      <c r="E30" s="2"/>
-      <c r="F30" s="2"/>
-      <c r="G30" s="2"/>
-      <c r="H30" s="2"/>
-      <c r="I30" s="2"/>
-      <c r="J30" s="4"/>
-      <c r="K30" s="2"/>
-      <c r="L30" s="2"/>
-    </row>
-    <row r="31" spans="1:12">
-      <c r="A31" s="2"/>
-      <c r="B31" s="2"/>
+        <v>Shortcut</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>694</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>695</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="I30" s="2">
+        <v>5</v>
+      </c>
+      <c r="J30" s="4">
+        <v>46298</v>
+      </c>
+      <c r="K30" s="2" t="s">
+        <v>593</v>
+      </c>
+      <c r="L30" s="2" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" ht="27">
+      <c r="A31" s="2" t="s">
+        <v>697</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>474</v>
+      </c>
       <c r="C31" s="5" t="str">
         <f>IF($B31="","",IFERROR(VLOOKUP($B31,'02_Конкуренты'!$A$4:$B$203,2,FALSE),"не найдено"))</f>
-        <v/>
-      </c>
-      <c r="D31" s="2"/>
-      <c r="E31" s="2"/>
-      <c r="F31" s="2"/>
-      <c r="G31" s="2"/>
-      <c r="H31" s="2"/>
-      <c r="I31" s="2"/>
-      <c r="J31" s="4"/>
-      <c r="K31" s="2"/>
-      <c r="L31" s="2"/>
-    </row>
-    <row r="32" spans="1:12">
-      <c r="A32" s="2"/>
-      <c r="B32" s="2"/>
+        <v>Numerous.ai</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>698</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>699</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>698</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>700</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="I31" s="2">
+        <v>4</v>
+      </c>
+      <c r="J31" s="4">
+        <v>46298</v>
+      </c>
+      <c r="K31" s="2" t="s">
+        <v>593</v>
+      </c>
+      <c r="L31" s="2" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" ht="27">
+      <c r="A32" s="2" t="s">
+        <v>702</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>474</v>
+      </c>
       <c r="C32" s="5" t="str">
         <f>IF($B32="","",IFERROR(VLOOKUP($B32,'02_Конкуренты'!$A$4:$B$203,2,FALSE),"не найдено"))</f>
-        <v/>
-      </c>
-      <c r="D32" s="2"/>
-      <c r="E32" s="2"/>
-      <c r="F32" s="2"/>
-      <c r="G32" s="2"/>
-      <c r="H32" s="2"/>
-      <c r="I32" s="2"/>
-      <c r="J32" s="4"/>
-      <c r="K32" s="2"/>
-      <c r="L32" s="2"/>
-    </row>
-    <row r="33" spans="1:12">
-      <c r="A33" s="2"/>
-      <c r="B33" s="2"/>
+        <v>Numerous.ai</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>703</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>699</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>703</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>704</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="I32" s="2">
+        <v>4</v>
+      </c>
+      <c r="J32" s="4">
+        <v>46298</v>
+      </c>
+      <c r="K32" s="2" t="s">
+        <v>593</v>
+      </c>
+      <c r="L32" s="2" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" ht="27">
+      <c r="A33" s="2" t="s">
+        <v>706</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>474</v>
+      </c>
       <c r="C33" s="5" t="str">
         <f>IF($B33="","",IFERROR(VLOOKUP($B33,'02_Конкуренты'!$A$4:$B$203,2,FALSE),"не найдено"))</f>
-        <v/>
-      </c>
-      <c r="D33" s="2"/>
-      <c r="E33" s="2"/>
-      <c r="F33" s="2"/>
-      <c r="G33" s="2"/>
-      <c r="H33" s="2"/>
-      <c r="I33" s="2"/>
-      <c r="J33" s="4"/>
-      <c r="K33" s="2"/>
-      <c r="L33" s="2"/>
-    </row>
-    <row r="34" spans="1:12">
-      <c r="A34" s="2"/>
-      <c r="B34" s="2"/>
+        <v>Numerous.ai</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>707</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>708</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>707</v>
+      </c>
+      <c r="G33" s="2" t="s">
+        <v>709</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="I33" s="2">
+        <v>5</v>
+      </c>
+      <c r="J33" s="4">
+        <v>46298</v>
+      </c>
+      <c r="K33" s="2" t="s">
+        <v>593</v>
+      </c>
+      <c r="L33" s="2" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" ht="40.5">
+      <c r="A34" s="2" t="s">
+        <v>711</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>293</v>
+      </c>
       <c r="C34" s="5" t="str">
         <f>IF($B34="","",IFERROR(VLOOKUP($B34,'02_Конкуренты'!$A$4:$B$203,2,FALSE),"не найдено"))</f>
-        <v/>
-      </c>
-      <c r="D34" s="2"/>
-      <c r="E34" s="2"/>
-      <c r="F34" s="2"/>
-      <c r="G34" s="2"/>
-      <c r="H34" s="2"/>
-      <c r="I34" s="2"/>
-      <c r="J34" s="4"/>
-      <c r="K34" s="2"/>
-      <c r="L34" s="2"/>
-    </row>
-    <row r="35" spans="1:12">
-      <c r="A35" s="2"/>
-      <c r="B35" s="2"/>
+        <v>PerfectXL</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>712</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>713</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>712</v>
+      </c>
+      <c r="G34" s="2" t="s">
+        <v>714</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="I34" s="2">
+        <v>5</v>
+      </c>
+      <c r="J34" s="4">
+        <v>46298</v>
+      </c>
+      <c r="K34" s="2" t="s">
+        <v>593</v>
+      </c>
+      <c r="L34" s="2" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" ht="27">
+      <c r="A35" s="2" t="s">
+        <v>716</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>293</v>
+      </c>
       <c r="C35" s="5" t="str">
         <f>IF($B35="","",IFERROR(VLOOKUP($B35,'02_Конкуренты'!$A$4:$B$203,2,FALSE),"не найдено"))</f>
-        <v/>
-      </c>
-      <c r="D35" s="2"/>
-      <c r="E35" s="2"/>
-      <c r="F35" s="2"/>
-      <c r="G35" s="2"/>
-      <c r="H35" s="2"/>
-      <c r="I35" s="2"/>
-      <c r="J35" s="4"/>
-      <c r="K35" s="2"/>
-      <c r="L35" s="2"/>
+        <v>PerfectXL</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>717</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>718</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>717</v>
+      </c>
+      <c r="G35" s="2" t="s">
+        <v>719</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="I35" s="2">
+        <v>4</v>
+      </c>
+      <c r="J35" s="4">
+        <v>46298</v>
+      </c>
+      <c r="K35" s="2" t="s">
+        <v>593</v>
+      </c>
+      <c r="L35" s="2" t="s">
+        <v>705</v>
+      </c>
     </row>
     <row r="36" spans="1:12">
       <c r="A36" s="2"/>
@@ -32243,7 +32805,7 @@
       </c>
       <c r="P4" s="7">
         <f>IF($A4="","",IFERROR(AVERAGEIF('03_Факты_сайта'!$B$4:$B$503,$A4,'03_Факты_сайта'!$I$4:$I$503),0))</f>
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="Q4" s="5" t="str">
         <f t="shared" ref="Q4:Q35" si="1">IF($A4="","",IF($O4&lt;0.5,"недостаточно данных",IF($P4&lt;3,"низкая доказательность",IF($O4&gt;=0.85,"готов к сравнению","требует дополнения"))))</f>
@@ -32300,7 +32862,7 @@
       </c>
       <c r="P5" s="7">
         <f>IF($A5="","",IFERROR(AVERAGEIF('03_Факты_сайта'!$B$4:$B$503,$A5,'03_Факты_сайта'!$I$4:$I$503),0))</f>
-        <v>4</v>
+        <v>4.333333333333333</v>
       </c>
       <c r="Q5" s="5" t="str">
         <f t="shared" si="1"/>
@@ -32357,7 +32919,7 @@
       </c>
       <c r="P6" s="7">
         <f>IF($A6="","",IFERROR(AVERAGEIF('03_Факты_сайта'!$B$4:$B$503,$A6,'03_Факты_сайта'!$I$4:$I$503),0))</f>
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="Q6" s="5" t="str">
         <f t="shared" si="1"/>
@@ -32414,7 +32976,7 @@
       </c>
       <c r="P7" s="7">
         <f>IF($A7="","",IFERROR(AVERAGEIF('03_Факты_сайта'!$B$4:$B$503,$A7,'03_Факты_сайта'!$I$4:$I$503),0))</f>
-        <v>4.666666666666667</v>
+        <v>4.75</v>
       </c>
       <c r="Q7" s="5" t="str">
         <f t="shared" si="1"/>
@@ -32471,7 +33033,7 @@
       </c>
       <c r="P8" s="7">
         <f>IF($A8="","",IFERROR(AVERAGEIF('03_Факты_сайта'!$B$4:$B$503,$A8,'03_Факты_сайта'!$I$4:$I$503),0))</f>
-        <v>5</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="Q8" s="5" t="str">
         <f t="shared" si="1"/>
@@ -32528,7 +33090,7 @@
       </c>
       <c r="P9" s="7">
         <f>IF($A9="","",IFERROR(AVERAGEIF('03_Факты_сайта'!$B$4:$B$503,$A9,'03_Факты_сайта'!$I$4:$I$503),0))</f>
-        <v>5</v>
+        <v>4.833333333333333</v>
       </c>
       <c r="Q9" s="5" t="str">
         <f t="shared" si="1"/>
@@ -32585,7 +33147,7 @@
       </c>
       <c r="P10" s="7">
         <f>IF($A10="","",IFERROR(AVERAGEIF('03_Факты_сайта'!$B$4:$B$503,$A10,'03_Факты_сайта'!$I$4:$I$503),0))</f>
-        <v>4.5</v>
+        <v>4.666666666666667</v>
       </c>
       <c r="Q10" s="5" t="str">
         <f t="shared" si="1"/>

--- a/ЛР5_Анализ_конкурентов/Excel/ЛР5_3_бизнес_модели_конкурентов_TableMind.xlsx
+++ b/ЛР5_Анализ_конкурентов/Excel/ЛР5_3_бизнес_модели_конкурентов_TableMind.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TableMind_EB\.claude\worktrees\handoff-continuation-57ce20\ЛР5_Анализ_конкурентов\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TableMind_EB\.claude\worktrees\handoff-project-continuation-447426\ЛР5_Анализ_конкурентов\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEEA5FFA-02E1-474C-B461-29F41E98DE1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD90DFC6-4EAB-4E31-86D2-E5453372CF4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2205" yWindow="458" windowWidth="12022" windowHeight="10972" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2648,7 +2648,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-66FD-40EB-8094-D882604E9355}"/>
+              <c16:uniqueId val="{00000000-2900-4B63-867A-92A2A19FEC9F}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
